--- a/VLT_params.xlsx
+++ b/VLT_params.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49CB6C99-80C0-469F-A9A4-11F9F507893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT-VBAL/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{49CB6C99-80C0-469F-A9A4-11F9F507893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2CE260-0F09-497C-B597-2129EDA14E92}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +60,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,9 +426,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,7 +439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -442,10 +447,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -453,10 +458,10 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -464,10 +469,10 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -475,10 +480,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -486,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
